--- a/education_forms/021_school_quality_survey--education_forms.xlsx
+++ b/education_forms/021_school_quality_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teaching_quality</t>
+          <t>teaching_quality_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teaching Quality</t>
+          <t>Teaching Quality 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -600,47 +600,47 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teaching_quality_what_improve</t>
+          <t>school_environment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What could be improved</t>
+          <t>School Environment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>school_environment</t>
+          <t>school_facilities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>School Environment</t>
+          <t>School Facilities</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_facilities</t>
+          <t>teacher_quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>School Facilities</t>
+          <t>Teacher Quality</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,46 +676,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>teacher_quality</t>
+          <t>teacher_helpfulness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Teacher Quality</t>
+          <t>Teacher Helpfulness</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>teacher_helpfulness</t>
+          <t>student_quality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Teacher Helpfulness</t>
+          <t>Student Quality</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>student_quality</t>
+          <t>school_leadership</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Student Quality</t>
+          <t>School Leadership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,46 +745,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_leadership</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>School Leadership</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>student_satisfaction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Student Satisfaction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>student_satisfaction</t>
+          <t>parent_satisfaction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Student Satisfaction</t>
+          <t>Parent Satisfaction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>parent_satisfaction</t>
+          <t>teacher_satisfaction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Parent Satisfaction</t>
+          <t>Teacher Satisfaction</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
+          <t>overall_quality_what_improvement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teacher Satisfaction</t>
+          <t>Overall Quality What Improvement</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>parent_satisfaction_what_improvement</t>
+          <t>overall_quality_what_improvement_what</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What could be improved</t>
+          <t>Overall Quality What Improvement What</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction_what_improvement</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>overall_quality_what_improvement_what_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What could be improved</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +919,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teaching_quality_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>teaching_quality_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teaching_quality_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>teaching_quality_choices</t>
+          <t>teaching_quality_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teaching_quality_choices</t>
+          <t>school_environment_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1250,46 +1043,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_environment_choices</t>
+          <t>school_facilities_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>school_environment_choices</t>
+          <t>school_facilities_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1179,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>teacher_helpfulness_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1230,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>student_quality_choices</t>
+          <t>teacher_helpfulness_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1383,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>school_leadership_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1434,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>student_satisfaction_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1485,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1502,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1519,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1536,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1553,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1570,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1587,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>parent_satisfaction_choices</t>
+          <t>teacher_satisfaction_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1621,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1638,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1862,46 +1655,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_4,_'value':_4}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': 4, 'value': 4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'label':_5,_'value':_5}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
